--- a/dondathang.xlsx
+++ b/dondathang.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3120" yWindow="2310" windowWidth="23625" windowHeight="13290" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2205" windowWidth="23625" windowHeight="13290" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Don dat hang" sheetId="1" state="visible" r:id="rId1"/>
@@ -77,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +118,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +176,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -309,6 +315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,19 +412,14 @@
     <author>System</author>
   </authors>
   <commentList>
+    <comment ref="Y10" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 146593.125 - Chênh lệch: -16287.875</t>
+      </text>
+    </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 162272.0 - Chênh lệch: 32454.399999999994</t>
-      </text>
-    </comment>
-    <comment ref="Y13" authorId="0" shapeId="0">
-      <text>
-        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 71014.0 - Chênh lệch: 14202.800000000003</t>
-      </text>
-    </comment>
-    <comment ref="Y20" authorId="0" shapeId="0">
-      <text>
-        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 59114.0 - Chênh lệch: 11822.800000000003</t>
+        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 146593.125 - Chênh lệch: -16287.875</t>
       </text>
     </comment>
   </commentList>
@@ -749,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV20"/>
+  <dimension ref="A1:AV13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7109375" customWidth="1" style="30" min="1" max="1"/>
@@ -803,8 +805,8 @@
     <col width="9.140625" customWidth="1" style="14" min="49" max="50"/>
     <col width="31.42578125" customWidth="1" style="14" min="51" max="51"/>
     <col width="13.7109375" customWidth="1" style="14" min="52" max="52"/>
-    <col width="9.140625" customWidth="1" style="14" min="53" max="1108"/>
-    <col width="9.140625" customWidth="1" style="14" min="1109" max="16384"/>
+    <col width="9.140625" customWidth="1" style="14" min="53" max="1109"/>
+    <col width="9.140625" customWidth="1" style="14" min="1110" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="45">
@@ -819,7 +821,7 @@
       <c r="E1" s="32" t="n"/>
       <c r="F1" s="32" t="n"/>
       <c r="G1" s="40" t="n">
-        <v>4069</v>
+        <v>4084</v>
       </c>
       <c r="H1" s="6" t="n"/>
       <c r="I1" s="33" t="n"/>
@@ -1373,7 +1375,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ĐĐHWINMART-4192677025</t>
+          <t>ĐĐHCOOP-102592451-00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1383,27 +1385,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1354-WMP_AMBIENT_CAN THO_FT - 1354 - WMP_AMBIENT_CAN THO_FT Đường 3A, Khu Công Nghiệp Sông Hậu – Giai Đoạn 1, Xã Châu Thành, TP. Cần Thơ TP. Cần Thơ Việt Nam</t>
+          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MN_MT_WIN1352</t>
+          <t>MB_MT_CF9167</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>WINMART PO4192677025 - Nguyễn Trọng Tùng (Admin)_0855004420_tungnt4@sup (Tổng trọng lượng: 13.9 kg)</t>
+          <t>COOPFOOD PO102592451-00 (Tổng trọng lượng: 182.4 kg)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WINMART PO4192677025 </t>
+          <t>COOPFOOD PO102592451-00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1418,7 +1420,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>LA_KHO2026</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1435,12 +1437,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="AV9" t="n">
@@ -1455,7 +1457,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ĐĐHWINMART-4192677025</t>
+          <t>ĐĐHCOOP-102592451-00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1465,32 +1467,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1354-WMP_AMBIENT_CAN THO_FT - 1354 - WMP_AMBIENT_CAN THO_FT Đường 3A, Khu Công Nghiệp Sông Hậu – Giai Đoạn 1, Xã Châu Thành, TP. Cần Thơ TP. Cần Thơ Việt Nam</t>
+          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MN_MT_WIN1352</t>
+          <t>MB_MT_CF9167</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>WINMART PO4192677025 - Nguyễn Trọng Tùng (Admin)_0855004420_tungnt4@sup</t>
+          <t>COOPFOOD PO102592451-00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>TP31630</t>
+          <t>TP30879_02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1505,14 +1507,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>LA_KHO2026</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>56811.2</v>
+        <v>12</v>
+      </c>
+      <c r="Y10" s="49" t="n">
+        <v>162881</v>
       </c>
       <c r="Z10">
         <f>Y10*X10</f>
@@ -1523,24 +1525,34 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>KM Bó Kèm - Che Barcode</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0879_0879_1</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Giảm 20%</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>13.9</v>
+        <v>45.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
         <v>60</v>
@@ -1549,12 +1561,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ĐĐHWINMART-4901304749</t>
+          <t>ĐĐHCOOP-102592451-00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1564,46 +1576,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
+          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MN_MT_WIN1326</t>
+          <t>MB_MT_CF9167</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>WINMART PO4901304749 (Tổng trọng lượng: 580.3 kg)</t>
+          <t>COOPFOOD PO102592451-00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>WINMART PO4901304749</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>TP_DN_1</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1616,13 +1633,24 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>DN</t>
-        </is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0879_0879_1</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3</v>
       </c>
       <c r="AV11" t="n">
         <v>60</v>
@@ -1631,12 +1659,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ĐĐHWINMART-4901304749</t>
+          <t>ĐĐHCOOP-102592451-00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1646,32 +1674,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
+          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MN_MT_WIN1326</t>
+          <t>MB_MT_CF9167</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>WINMART PO4901304749</t>
+          <t>COOPFOOD PO102592451-00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>TP31203</t>
+          <t>TP30886_02</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Nước Giặt Blue kháng khuẩn hương hoa thạch thảo 3.2L</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1686,14 +1714,14 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>TP_DN_1</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y12" s="46" t="n">
-        <v>162272</v>
+        <v>12</v>
+      </c>
+      <c r="Y12" s="49" t="n">
+        <v>162881</v>
       </c>
       <c r="Z12">
         <f>Y12*X12</f>
@@ -1704,24 +1732,34 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>DN</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>KM Bó Kèm - Che Barcode</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0886_0886_1</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Giảm 20%</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>27.8</v>
+        <v>45.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
         <v>60</v>
@@ -1730,12 +1768,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ĐĐHWINMART-4901304749</t>
+          <t>ĐĐHCOOP-102592451-00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1745,32 +1783,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
+          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MN_MT_WIN1326</t>
+          <t>MB_MT_CF9167</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>WINMART PO4901304749</t>
+          <t>COOPFOOD PO102592451-00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>TP31630</t>
+          <t>TP30886_02</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1780,760 +1818,48 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>TP_DN_1</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X13" t="n">
         <v>12</v>
       </c>
-      <c r="Y13" s="46" t="n">
-        <v>71014</v>
-      </c>
-      <c r="Z13">
-        <f>Y13*X13</f>
-        <v/>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>Giảm 20%</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0886_0886_1</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>41.7</v>
+        <v>45.6</v>
       </c>
       <c r="AU13" t="n">
         <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>TP32767</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Nước lau sàn Blue Hương Lavender túi 3.5kg</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>71600</v>
-      </c>
-      <c r="Z14">
-        <f>Y14*X14</f>
-        <v/>
-      </c>
-      <c r="AE14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>KM Giao Rời - Không Che</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>1+1 {KM Giao Rời - Không che barcode}</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>TP32767</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Nước lau sàn Blue Hương Lavender túi 3.5kg</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>TP30879_02</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X16" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>145000</v>
-      </c>
-      <c r="Z16">
-        <f>Y16*X16</f>
-        <v/>
-      </c>
-      <c r="AE16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>KM Bó Kèm + Che barcode</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>0879_0879_1</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>1+1  {KM Bó Kèm + Che barcode}</t>
-        </is>
-      </c>
-      <c r="AT16" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>TP30879_02</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>0879_0879_1</t>
-        </is>
-      </c>
-      <c r="AT17" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>TP30886_02</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>145000</v>
-      </c>
-      <c r="Z18">
-        <f>Y18*X18</f>
-        <v/>
-      </c>
-      <c r="AE18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>KM Bó Kèm + Che barcode</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>0886_0886_1</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>1+1  {KM Bó Kèm + Che barcode}</t>
-        </is>
-      </c>
-      <c r="AT18" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>TP30886_02</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X19" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>0886_0886_1</t>
-        </is>
-      </c>
-      <c r="AT19" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ĐĐHWINMART-4901304749</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1325-WMP_AMBIENT_DA NANG_FT - 1325 - WMP_AMBIENT_DA NANG_FT Đường số 6 KCN Hòa Khánh TP. Đà Nẵng Việt Nam</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MN_MT_WIN1326</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>WINMART PO4901304749</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>TP30473</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>TP_DN_1</t>
-        </is>
-      </c>
-      <c r="X20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y20" s="46" t="n">
-        <v>59114</v>
-      </c>
-      <c r="Z20">
-        <f>Y20*X20</f>
-        <v/>
-      </c>
-      <c r="AE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>MT_MN</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>DN</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Giảm 20%
-</t>
-        </is>
-      </c>
-      <c r="AT20" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV20" t="n">
         <v>60</v>
       </c>
     </row>

--- a/dondathang.xlsx
+++ b/dondathang.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2205" windowWidth="23625" windowHeight="13290" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Don dat hang" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Don dat hang" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="SAVoucher">#REF!</definedName>
@@ -404,26 +404,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>System</author>
-  </authors>
-  <commentList>
-    <comment ref="Y10" authorId="0" shapeId="0">
-      <text>
-        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 146593.125 - Chênh lệch: -16287.875</t>
-      </text>
-    </comment>
-    <comment ref="Y12" authorId="0" shapeId="0">
-      <text>
-        <t>Kiểm tra lại giá mã này! - Giá hóa đơn: 146593.125 - Chênh lệch: -16287.875</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -751,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV13"/>
+  <dimension ref="A1:AV11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7109375" customWidth="1" style="30" min="1" max="1"/>
@@ -821,7 +801,7 @@
       <c r="E1" s="32" t="n"/>
       <c r="F1" s="32" t="n"/>
       <c r="G1" s="40" t="n">
-        <v>4084</v>
+        <v>4114</v>
       </c>
       <c r="H1" s="6" t="n"/>
       <c r="I1" s="33" t="n"/>
@@ -1370,12 +1350,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ĐĐHCOOP-102592451-00</t>
+          <t>ĐĐHSATRA-P-005484027</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1385,27 +1365,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
+          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MB_MT_CF9167</t>
+          <t>MN_MT_STF1150</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>COOPFOOD PO102592451-00 (Tổng trọng lượng: 182.4 kg)</t>
+          <t>SATRA P-005484027  (Tổng trọng lượng: 30.4 kg)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>COOPFOOD PO102592451-00</t>
+          <t>SATRA P-005484027</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1420,7 +1400,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>TP_HN_12</t>
+          <t>LA_TP</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1437,12 +1417,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>MT_MB</t>
+          <t>MT_MN</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="AV9" t="n">
@@ -1452,12 +1432,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ĐĐHCOOP-102592451-00</t>
+          <t>ĐĐHSATRA-P-005484027</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1467,32 +1447,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
+          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MB_MT_CF9167</t>
+          <t>MN_MT_STF1150</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>COOPFOOD PO102592451-00</t>
+          <t xml:space="preserve">SATRA P-005484027 </t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>TP30879_02</t>
+          <t>TP30985_02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1507,14 +1487,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>TP_HN_12</t>
+          <t>LA_TP</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y10" s="49" t="n">
-        <v>162881</v>
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>107100</v>
       </c>
       <c r="Z10">
         <f>Y10*X10</f>
@@ -1525,34 +1505,24 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>MT_MB</t>
+          <t>MT_MN</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>KM Bó Kèm - Che Barcode</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0879_0879_1</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>Giảm 40%</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>45.6</v>
+        <v>15.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
         <v>60</v>
@@ -1561,12 +1531,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ĐĐHCOOP-102592451-00</t>
+          <t>ĐĐHSATRA-P-005484027</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1576,32 +1546,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
+          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MB_MT_CF9167</t>
+          <t>MN_MT_STF1150</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>COOPFOOD PO102592451-00</t>
+          <t xml:space="preserve">SATRA P-005484027 </t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>TP30879_02</t>
+          <t>TP30992_02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1611,255 +1581,49 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>TP_HN_12</t>
+          <t>LA_TP</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
+        <v>107100</v>
+      </c>
+      <c r="Z11">
+        <f>Y11*X11</f>
+        <v/>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>MT_MB</t>
+          <t>MT_MN</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0879_0879_1</t>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Giảm 40%</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>45.6</v>
+        <v>15.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ĐĐHCOOP-102592451-00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MB_MT_CF9167</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>COOPFOOD PO102592451-00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>TP30886_02</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>TP_HN_12</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y12" s="49" t="n">
-        <v>162881</v>
-      </c>
-      <c r="Z12">
-        <f>Y12*X12</f>
-        <v/>
-      </c>
-      <c r="AE12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>MT_MB</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>KM Bó Kèm - Che Barcode</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>0886_0886_1</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>1+1</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ĐĐHCOOP-102592451-00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>09167-CF HN YEN NGHIA - B9 - Lô B- TT2, dự án khu nhà ở Bộ tư lệnh Thủ Đô, phường Yên Nghĩa, Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MB_MT_CF9167</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>COOPFOOD PO102592451-00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>TP30886_02</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>TP_HN_12</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>MT_MB</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0886_0886_1</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV13" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1917,7 +1681,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/dondathang.xlsx
+++ b/dondathang.xlsx
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV11"/>
+  <dimension ref="A1:AV84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7109375" customWidth="1" style="30" min="1" max="1"/>
@@ -801,7 +801,7 @@
       <c r="E1" s="32" t="n"/>
       <c r="F1" s="32" t="n"/>
       <c r="G1" s="40" t="n">
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="H1" s="6" t="n"/>
       <c r="I1" s="33" t="n"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ĐĐHSATRA-P-005484027</t>
+          <t>ĐĐHBIGC-2628057223860</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1365,27 +1365,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
+          <t>LINFOX WAREHOUSE (802)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MN_MT_STF1150</t>
+          <t>MB_MT_BIGC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SATRA P-005484027  (Tổng trọng lượng: 30.4 kg)</t>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 13.08 tấn)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>SATRA P-005484027</t>
+          <t>BIGC PO2628057223860</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>LA_TP</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1417,12 +1417,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>BIGCANLAC</t>
         </is>
       </c>
       <c r="AV9" t="n">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ĐĐHSATRA-P-005484027</t>
+          <t>ĐĐHBIGC-2628057223860</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1447,32 +1452,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
+          <t>LINFOX WAREHOUSE (802)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MN_MT_STF1150</t>
+          <t>MB_MT_BIGC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SATRA P-005484027 </t>
+          <t>BIGC PO2628057223860</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>TP30985_02</t>
+          <t>TP30879_02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1487,14 +1492,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>LA_TP</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="Y10" t="n">
-        <v>107100</v>
+        <v>148750</v>
       </c>
       <c r="Z10">
         <f>Y10*X10</f>
@@ -1505,24 +1510,31 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Giảm 40%</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
+        <v>456.0000000000001</v>
       </c>
       <c r="AV10" t="n">
         <v>60</v>
@@ -1536,7 +1548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ĐĐHSATRA-P-005484027</t>
+          <t>ĐĐHBIGC-2628057223860</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,32 +1558,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3/1 Nguyễn Thị Định, Phường Bình Trưng,HCM,VNM</t>
+          <t>LINFOX WAREHOUSE (802)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MN_MT_STF1150</t>
+          <t>MB_MT_BIGC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SATRA P-005484027 </t>
+          <t>BIGC PO2628057223860</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>TP30992_02</t>
+          <t>TP30879_02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1581,49 +1593,7380 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>LA_TP</t>
+          <t>TP_HN_12</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="Y11" t="n">
-        <v>107100</v>
-      </c>
-      <c r="Z11">
-        <f>Y11*X11</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>MT_MN</t>
+          <t>MT_MB</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Giảm 40%</t>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
         </is>
       </c>
       <c r="AT11" t="n">
+        <v>456.0000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z12">
+        <f>Y12*X12</f>
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z14">
+        <f>Y14*X14</f>
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>278</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>278</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z16">
+        <f>Y16*X16</f>
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>278</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>278</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 1.82 tấn)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z18">
+        <f>Y18*X18</f>
+        <v/>
+      </c>
+      <c r="AE18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>456.0000000000001</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>456.0000000000001</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z20">
+        <f>Y20*X20</f>
+        <v/>
+      </c>
+      <c r="AE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>456.0000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>BIGCTHANGLONG</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>456.0000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 195.0 kg)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>TP30466</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất đậu xanh túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z22">
+        <f>Y22*X22</f>
+        <v/>
+      </c>
+      <c r="AE22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>BIGCHAIPHONG</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>69.00000000000001</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>BIGCHAIPHONG</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z24">
+        <f>Y24*X24</f>
+        <v/>
+      </c>
+      <c r="AE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>BIGCHAIPHONG</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>69.00000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>BIGCHAIPHONG</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 56.88 kg)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>HH00527</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Nước xả vải Joeunmiso 1.3l hương Đại Dương</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>37554.7</v>
+      </c>
+      <c r="Z26">
+        <f>Y26*X26</f>
+        <v/>
+      </c>
+      <c r="AE26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>BIGCGARDEN</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giảm giá 15% +</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>TP30466</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất đậu xanh túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z27">
+        <f>Y27*X27</f>
+        <v/>
+      </c>
+      <c r="AE27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>BIGCGARDEN</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>BIGCGARDEN</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z29">
+        <f>Y29*X29</f>
+        <v/>
+      </c>
+      <c r="AE29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>BIGCGARDEN</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>BIGCGARDEN</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 130.7 kg)</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z31">
+        <f>Y31*X31</f>
+        <v/>
+      </c>
+      <c r="AE31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z33">
+        <f>Y33*X33</f>
+        <v/>
+      </c>
+      <c r="AE33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z35">
+        <f>Y35*X35</f>
+        <v/>
+      </c>
+      <c r="AE35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>BIGCNAMDINH</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 5.82 tấn)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z37">
+        <f>Y37*X37</f>
+        <v/>
+      </c>
+      <c r="AE37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z39">
+        <f>Y39*X39</f>
+        <v/>
+      </c>
+      <c r="AE39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>760</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z41">
+        <f>Y41*X41</f>
+        <v/>
+      </c>
+      <c r="AE41" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>695</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>695</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z43">
+        <f>Y43*X43</f>
+        <v/>
+      </c>
+      <c r="AE43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>695</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>695</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 19.5 kg)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z45">
+        <f>Y45*X45</f>
+        <v/>
+      </c>
+      <c r="AE45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>BIGCLONGBIEN</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 69.4 kg)</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z47">
+        <f>Y47*X47</f>
+        <v/>
+      </c>
+      <c r="AE47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
         <v>15.2</v>
       </c>
-      <c r="AU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AV47" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>TP30466</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất đậu xanh túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z49">
+        <f>Y49*X49</f>
+        <v/>
+      </c>
+      <c r="AE49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z51">
+        <f>Y51*X51</f>
+        <v/>
+      </c>
+      <c r="AE51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>BIGCTHANHHOA</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 39.0 kg)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z53">
+        <f>Y53*X53</f>
+        <v/>
+      </c>
+      <c r="AE53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>BIGCNINHBINH</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>BIGCNINHBINH</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 139.0 kg)</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z55">
+        <f>Y55*X55</f>
+        <v/>
+      </c>
+      <c r="AE55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>BIGCHALONG</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>TP31647</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue Không Mùi túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>BIGCHALONG</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 19.5 kg)</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z57">
+        <f>Y57*X57</f>
+        <v/>
+      </c>
+      <c r="AE57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>BIGCLETRONGTAN</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>BIGCLETRONGTAN</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 336.8 kg)</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z59">
+        <f>Y59*X59</f>
+        <v/>
+      </c>
+      <c r="AE59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>TP30886_02</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Nước Hoa túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z61">
+        <f>Y61*X61</f>
+        <v/>
+      </c>
+      <c r="AE61" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AT62" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z63">
+        <f>Y63*X63</f>
+        <v/>
+      </c>
+      <c r="AE63" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>TP30763_1</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Viên Giặt xả Blue Muối Hồng túi 13g x 48</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>173864</v>
+      </c>
+      <c r="Z65">
+        <f>Y65*X65</f>
+        <v/>
+      </c>
+      <c r="AE65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AT65" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z66">
+        <f>Y66*X66</f>
+        <v/>
+      </c>
+      <c r="AE66" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>BIGCTHAINGUYEN</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 75.2 kg)</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z68">
+        <f>Y68*X68</f>
+        <v/>
+      </c>
+      <c r="AE68" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>BIGCLAOCAI</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>BIGCLAOCAI</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z70">
+        <f>Y70*X70</f>
+        <v/>
+      </c>
+      <c r="AE70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>BIGCLAOCAI</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>BIGCLAOCAI</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>TP31036</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Nước thông tắc cống Blue 1000ml</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>41379.7</v>
+      </c>
+      <c r="Z72">
+        <f>Y72*X72</f>
+        <v/>
+      </c>
+      <c r="AE72" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>BIGCLAOCAI</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM GIÁ 15%
+</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 30.4 kg)</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>148750</v>
+      </c>
+      <c r="Z73">
+        <f>Y73*X73</f>
+        <v/>
+      </c>
+      <c r="AE73" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>BIGCHANAM</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>TP30879_02</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Đậm đặc Hương Thảo Mộc túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>BIGCHANAM</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 27.8 kg)</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>73545</v>
+      </c>
+      <c r="Z75">
+        <f>Y75*X75</f>
+        <v/>
+      </c>
+      <c r="AE75" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>BIGCHUNGYEN</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>TP31630</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue hương Chanh túi 3.2L (QC*4)</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>BIGCHUNGYEN</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860 (Tổng trọng lượng: 748.5 kg)</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z77">
+        <f>Y77*X77</f>
+        <v/>
+      </c>
+      <c r="AE77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>76</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>TP30985_02</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Thanh Xuân Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>76</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>162273</v>
+      </c>
+      <c r="Z79">
+        <f>Y79*X79</f>
+        <v/>
+      </c>
+      <c r="AE79" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>1+1</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>152</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>TP30992_02</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Nước giặt xả Blue Deep Clean Hương Phấn Hồng Túi 3.6L</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>152</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>TP30466</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất đậu xanh túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z81">
+        <f>Y81*X81</f>
+        <v/>
+      </c>
+      <c r="AE81" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>69.00000000000001</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X82" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>TP30473</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo túi 2.1L (QC*6)</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>38424.1</v>
+      </c>
+      <c r="Z83">
+        <f>Y83*X83</f>
+        <v/>
+      </c>
+      <c r="AE83" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>KM Rời - Không Che Barcode</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GIẢM 35% + Tặng 1 túi NRC gạo 800ml TP30343 </t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>138</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ĐĐHBIGC-2628057223860</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LINFOX WAREHOUSE (802)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MB_MT_BIGC</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BIGC PO2628057223860</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>TP30343</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Nước rửa chén Blue chiết xuất gạo 800g</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>TP_HN_12</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>MT_MB</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>BIGCYENBAI</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>57</v>
+      </c>
+      <c r="AV84" t="n">
         <v>60</v>
       </c>
     </row>
